--- a/Sprint 10/dades_GrupB.xlsx
+++ b/Sprint 10/dades_GrupB.xlsx
@@ -669,7 +669,7 @@
         <v>38648</v>
       </c>
       <c r="P3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>21115</v>
       </c>
       <c r="P32" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>36821</v>
       </c>
       <c r="P154" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>25864</v>
       </c>
       <c r="P312" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q312" t="inlineStr">
         <is>

--- a/Sprint 10/dades_GrupB.xlsx
+++ b/Sprint 10/dades_GrupB.xlsx
@@ -3161,7 +3161,7 @@
         <v>25510</v>
       </c>
       <c r="P35" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>22943</v>
       </c>
       <c r="P62" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>34268</v>
       </c>
       <c r="P143" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>37555</v>
       </c>
       <c r="P198" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>27700</v>
       </c>
       <c r="P204" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
